--- a/Result/14-12-24/NASDAQstock_14-12-24period252RS90.xlsx
+++ b/Result/14-12-24/NASDAQstock_14-12-24period252RS90.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/14-12-24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371377EA-4407-E54D-BA3C-C3C52EA2F2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3109040-F888-8445-9422-07522F963CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -815,18 +815,21 @@
       <b/>
       <sz val="11"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
     </font>
     <font>
@@ -837,7 +840,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -860,6 +863,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFA500"/>
         <bgColor rgb="FFFFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -890,7 +899,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -900,6 +909,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1569,7 +1579,7 @@
       </c>
     </row>
     <row r="4" spans="1:40">
-      <c r="A4" t="s">
+      <c r="A4" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B4">
@@ -2164,7 +2174,7 @@
       </c>
     </row>
     <row r="9" spans="1:40">
-      <c r="A9" t="s">
+      <c r="A9" s="7" t="s">
         <v>67</v>
       </c>
       <c r="B9">
@@ -2283,7 +2293,7 @@
       </c>
     </row>
     <row r="10" spans="1:40">
-      <c r="A10" t="s">
+      <c r="A10" s="7" t="s">
         <v>70</v>
       </c>
       <c r="B10">
@@ -2402,7 +2412,7 @@
       </c>
     </row>
     <row r="11" spans="1:40">
-      <c r="A11" t="s">
+      <c r="A11" s="7" t="s">
         <v>74</v>
       </c>
       <c r="B11">
@@ -3473,7 +3483,7 @@
       </c>
     </row>
     <row r="20" spans="1:40">
-      <c r="A20" t="s">
+      <c r="A20" s="7" t="s">
         <v>96</v>
       </c>
       <c r="B20">
@@ -3830,7 +3840,7 @@
       </c>
     </row>
     <row r="23" spans="1:40">
-      <c r="A23" t="s">
+      <c r="A23" s="7" t="s">
         <v>103</v>
       </c>
       <c r="B23">
@@ -4068,7 +4078,7 @@
       </c>
     </row>
     <row r="25" spans="1:40">
-      <c r="A25" t="s">
+      <c r="A25" s="7" t="s">
         <v>108</v>
       </c>
       <c r="B25">
@@ -4904,7 +4914,7 @@
       </c>
     </row>
     <row r="32" spans="1:40">
-      <c r="A32" t="s">
+      <c r="A32" s="7" t="s">
         <v>123</v>
       </c>
       <c r="B32">
@@ -8117,7 +8127,7 @@
       </c>
     </row>
     <row r="59" spans="1:40">
-      <c r="A59" t="s">
+      <c r="A59" s="7" t="s">
         <v>168</v>
       </c>
       <c r="B59">
@@ -10973,7 +10983,7 @@
       </c>
     </row>
     <row r="83" spans="1:40">
-      <c r="A83" t="s">
+      <c r="A83" s="7" t="s">
         <v>211</v>
       </c>
       <c r="B83">
